--- a/artfynd/A 28409-2025 artfynd.xlsx
+++ b/artfynd/A 28409-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,6 +910,3446 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126591605</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>744004</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7175058</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126591575</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>744313</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7174751</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126591585</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>744412</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7174653</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126591594</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>744342</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7174693</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar, flera träd</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126591593</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>744415</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7174604</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar, flera träd</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126591569</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58354</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>744456</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7174718</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flög upp på en gren i en senvuxen liten gran, kollade på mig, sket, och flög iväg</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126591591</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>744030</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7175064</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126591577</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>744053</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7174888</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126591604</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78647</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>353</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>744160</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7174857</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126591592</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>744476</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7174709</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långa bålar, rikligt</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126591572</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>744516</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7174708</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126591602</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>744018</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7175088</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126591581</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>744010</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7175003</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126591579</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>744008</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7175023</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126591584</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>744015</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7175028</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126591601</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>744042</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7175019</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126591570</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91210</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>744081</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7174948</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126591571</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>744475</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7174723</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126591578</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>744081</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7174948</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126591576</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>744244</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7174800</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126591580</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>744013</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7175001</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126591597</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>744119</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7174920</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långa bålar, rikligt</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126591573</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>744392</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7174607</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126591599</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>744069</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7174983</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126591583</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>744054</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7174882</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126591590</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>744042</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7174988</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126591574</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>744358</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7174698</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126591589</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91866</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>744331</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7174735</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126591600</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>744023</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7175031</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126591596</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>744142</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7174925</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126591595</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>744154</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7174866</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126591586</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>744358</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7174698</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126591598</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svarthultmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>744081</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7174948</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28409-2025 artfynd.xlsx
+++ b/artfynd/A 28409-2025 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>126591605</v>
       </c>
       <c r="B4" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126591585</v>
+        <v>126591594</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,31 +1020,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>744412</v>
+        <v>744342</v>
       </c>
       <c r="R5" t="n">
-        <v>7174653</v>
+        <v>7174693</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,12 +1085,18 @@
           <t>2025-07-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar, flera träd</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1114,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126591594</v>
+        <v>126591575</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,26 +1126,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>744342</v>
+        <v>744313</v>
       </c>
       <c r="R6" t="n">
-        <v>7174693</v>
+        <v>7174751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1198,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt, långa bålar, flera träd</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1207,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126591575</v>
+        <v>126591585</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,7 +1258,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>744313</v>
+        <v>744412</v>
       </c>
       <c r="R7" t="n">
-        <v>7174751</v>
+        <v>7174653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,11 +1304,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126591604</v>
+        <v>126591569</v>
       </c>
       <c r="B8" t="n">
-        <v>78647</v>
+        <v>58354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,34 +1341,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>103056</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>744160</v>
+        <v>744456</v>
       </c>
       <c r="R8" t="n">
-        <v>7174857</v>
+        <v>7174718</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,6 +1417,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flög upp på en gren i en senvuxen liten gran, kollade på mig, sket, och flög iväg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126591577</v>
+        <v>126591604</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>78678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,42 +1459,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>744053</v>
+        <v>744160</v>
       </c>
       <c r="R9" t="n">
-        <v>7174888</v>
+        <v>7174857</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,11 +1519,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126591569</v>
+        <v>126591577</v>
       </c>
       <c r="B10" t="n">
-        <v>58354</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,37 +1556,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103056</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>744456</v>
+        <v>744053</v>
       </c>
       <c r="R10" t="n">
-        <v>7174718</v>
+        <v>7174888</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flög upp på en gren i en senvuxen liten gran, kollade på mig, sket, och flög iväg</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,7 +1658,7 @@
         <v>126591591</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>126591593</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126591592</v>
+        <v>126591572</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,26 +1874,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1901,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>744476</v>
+        <v>744516</v>
       </c>
       <c r="R13" t="n">
-        <v>7174709</v>
+        <v>7174708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långa bålar, rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,7 +1955,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126591572</v>
+        <v>126591592</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,31 +1984,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2012,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>744516</v>
+        <v>744476</v>
       </c>
       <c r="R14" t="n">
-        <v>7174708</v>
+        <v>7174709</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2051,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långa bålar, rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,6 +2060,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>126591602</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>126591570</v>
       </c>
       <c r="B19" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>126591601</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>126591571</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>126591597</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>126591599</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>126591590</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126591574</v>
+        <v>126591589</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>91940</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3658,42 +3658,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5454</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>744358</v>
+        <v>744331</v>
       </c>
       <c r="R30" t="n">
-        <v>7174698</v>
+        <v>7174735</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,11 +3718,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3757,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126591589</v>
+        <v>126591574</v>
       </c>
       <c r="B31" t="n">
-        <v>91866</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3768,34 +3755,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5454</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>744331</v>
+        <v>744358</v>
       </c>
       <c r="R31" t="n">
-        <v>7174735</v>
+        <v>7174698</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,6 +3823,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3857,7 +3857,7 @@
         <v>126591600</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3951,10 +3951,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126591596</v>
+        <v>126591595</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>744142</v>
+        <v>744154</v>
       </c>
       <c r="R33" t="n">
-        <v>7174925</v>
+        <v>7174866</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4022,11 +4022,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4053,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126591595</v>
+        <v>126591596</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4088,10 +4083,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>744154</v>
+        <v>744142</v>
       </c>
       <c r="R34" t="n">
-        <v>7174866</v>
+        <v>7174925</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4124,6 +4119,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4258,7 +4258,7 @@
         <v>126591598</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28409-2025 artfynd.xlsx
+++ b/artfynd/A 28409-2025 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>126591605</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>80152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>126591594</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126591569</v>
+        <v>126591591</v>
       </c>
       <c r="B8" t="n">
-        <v>58354</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,50 +1341,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103056</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>744456</v>
+        <v>744030</v>
       </c>
       <c r="R8" t="n">
-        <v>7174718</v>
+        <v>7175064</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1405,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flög upp på en gren i en senvuxen liten gran, kollade på mig, sket, och flög iväg</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,7 +1435,7 @@
         <v>126591604</v>
       </c>
       <c r="B9" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126591577</v>
+        <v>126591593</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,31 +1540,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1588,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>744053</v>
+        <v>744415</v>
       </c>
       <c r="R10" t="n">
-        <v>7174888</v>
+        <v>7174604</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1607,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt, långa bålar, flera träd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,6 +1616,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1655,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126591591</v>
+        <v>126591577</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,34 +1646,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>744030</v>
+        <v>744053</v>
       </c>
       <c r="R11" t="n">
-        <v>7175064</v>
+        <v>7174888</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126591593</v>
+        <v>126591569</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>58354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,26 +1756,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103056</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>744415</v>
+        <v>744456</v>
       </c>
       <c r="R12" t="n">
-        <v>7174604</v>
+        <v>7174718</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt, långa bålar, flera träd</t>
+          <t>Flög upp på en gren i en senvuxen liten gran, kollade på mig, sket, och flög iväg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1844,7 +1845,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126591572</v>
+        <v>126591592</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,31 +1874,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1906,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>744516</v>
+        <v>744476</v>
       </c>
       <c r="R13" t="n">
-        <v>7174708</v>
+        <v>7174709</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1941,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långa bålar, rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,6 +1950,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1973,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126591592</v>
+        <v>126591572</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,26 +1980,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2011,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>744476</v>
+        <v>744516</v>
       </c>
       <c r="R14" t="n">
-        <v>7174709</v>
+        <v>7174708</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2052,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långa bålar, rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,7 +2061,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>126591602</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126591584</v>
+        <v>126591581</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,21 +2192,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,7 +2214,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>744015</v>
+        <v>744010</v>
       </c>
       <c r="R16" t="n">
-        <v>7175028</v>
+        <v>7175003</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,6 +2260,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126591581</v>
+        <v>126591579</v>
       </c>
       <c r="B17" t="n">
         <v>57657</v>
@@ -2329,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>744010</v>
+        <v>744008</v>
       </c>
       <c r="R17" t="n">
-        <v>7175003</v>
+        <v>7175023</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2396,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126591579</v>
+        <v>126591584</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2429,7 +2434,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>744008</v>
+        <v>744015</v>
       </c>
       <c r="R18" t="n">
-        <v>7175023</v>
+        <v>7175028</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,11 +2480,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2509,7 @@
         <v>126591570</v>
       </c>
       <c r="B19" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>126591601</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>126591571</v>
       </c>
       <c r="B21" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>126591597</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>126591599</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>126591590</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>126591589</v>
       </c>
       <c r="B30" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>126591600</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>126591595</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>126591596</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126591586</v>
+        <v>126591598</v>
       </c>
       <c r="B35" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4161,42 +4161,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>744358</v>
+        <v>744081</v>
       </c>
       <c r="R35" t="n">
-        <v>7174698</v>
+        <v>7174948</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4255,10 +4247,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126591598</v>
+        <v>126591586</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>57817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4266,34 +4258,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>744081</v>
+        <v>744358</v>
       </c>
       <c r="R36" t="n">
-        <v>7174948</v>
+        <v>7174698</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 28409-2025 artfynd.xlsx
+++ b/artfynd/A 28409-2025 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126591575</v>
+        <v>126591585</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,7 +1148,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>744313</v>
+        <v>744412</v>
       </c>
       <c r="R6" t="n">
-        <v>7174751</v>
+        <v>7174653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,11 +1194,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126591585</v>
+        <v>126591575</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,7 +1253,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>744412</v>
+        <v>744313</v>
       </c>
       <c r="R7" t="n">
-        <v>7174653</v>
+        <v>7174751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,6 +1299,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126591604</v>
+        <v>126591593</v>
       </c>
       <c r="B9" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,34 +1443,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>744160</v>
+        <v>744415</v>
       </c>
       <c r="R9" t="n">
-        <v>7174857</v>
+        <v>7174604</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,12 +1508,18 @@
           <t>2025-07-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar, flera träd</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1529,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126591593</v>
+        <v>126591577</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,26 +1549,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1567,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>744415</v>
+        <v>744053</v>
       </c>
       <c r="R10" t="n">
-        <v>7174604</v>
+        <v>7174888</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1621,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt, långa bålar, flera träd</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,7 +1630,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1635,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126591577</v>
+        <v>126591569</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>58354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,29 +1659,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103056</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1678,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>744053</v>
+        <v>744456</v>
       </c>
       <c r="R11" t="n">
-        <v>7174888</v>
+        <v>7174718</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1739,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Flög upp på en gren i en senvuxen liten gran, kollade på mig, sket, och flög iväg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126591569</v>
+        <v>126591604</v>
       </c>
       <c r="B12" t="n">
-        <v>58354</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,50 +1777,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103056</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svarthultmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>744456</v>
+        <v>744160</v>
       </c>
       <c r="R12" t="n">
-        <v>7174718</v>
+        <v>7174857</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,11 +1837,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Flög upp på en gren i en senvuxen liten gran, kollade på mig, sket, och flög iväg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126591592</v>
+        <v>126591572</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,26 +1874,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1901,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>744476</v>
+        <v>744516</v>
       </c>
       <c r="R13" t="n">
-        <v>7174709</v>
+        <v>7174708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1946,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långa bålar, rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,7 +1955,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126591572</v>
+        <v>126591592</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,31 +1984,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2012,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>744516</v>
+        <v>744476</v>
       </c>
       <c r="R14" t="n">
-        <v>7174708</v>
+        <v>7174709</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2051,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Långa bålar, rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,6 +2060,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126591581</v>
+        <v>126591584</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,21 +2192,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,7 +2214,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>744010</v>
+        <v>744015</v>
       </c>
       <c r="R16" t="n">
-        <v>7175003</v>
+        <v>7175028</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,11 +2260,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126591579</v>
+        <v>126591581</v>
       </c>
       <c r="B17" t="n">
         <v>57657</v>
@@ -2334,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>744008</v>
+        <v>744010</v>
       </c>
       <c r="R17" t="n">
-        <v>7175023</v>
+        <v>7175003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126591584</v>
+        <v>126591579</v>
       </c>
       <c r="B18" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2434,7 +2429,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>744015</v>
+        <v>744008</v>
       </c>
       <c r="R18" t="n">
-        <v>7175028</v>
+        <v>7175023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,6 +2475,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,32 +2506,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126591570</v>
+        <v>126591601</v>
       </c>
       <c r="B19" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>744081</v>
+        <v>744042</v>
       </c>
       <c r="R19" t="n">
-        <v>7174948</v>
+        <v>7175019</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,32 +2603,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126591601</v>
+        <v>126591570</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>744042</v>
+        <v>744081</v>
       </c>
       <c r="R20" t="n">
-        <v>7175019</v>
+        <v>7174948</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126591580</v>
+        <v>126591576</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2940,7 +2940,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>744013</v>
+        <v>744244</v>
       </c>
       <c r="R23" t="n">
-        <v>7175001</v>
+        <v>7174800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,7 +3017,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126591576</v>
+        <v>126591580</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -3050,7 +3050,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>744244</v>
+        <v>744013</v>
       </c>
       <c r="R24" t="n">
-        <v>7174800</v>
+        <v>7175001</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
